--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488021_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488021_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6339</v>
+        <v>10.6921</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8485</v>
+        <v>9.075200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7853</v>
+        <v>1.6169</v>
       </c>
       <c r="G2" t="n">
         <v>8.529500000000001</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.575</v>
+        <v>-0.5168</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0365</v>
+        <v>0.1901</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5384</v>
+        <v>-0.7069</v>
       </c>
       <c r="V2" t="n">
         <v>0.8953</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.243600000000001</v>
+        <v>8.926600000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.046</v>
+        <v>4.7009</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1976</v>
+        <v>4.2257</v>
       </c>
       <c r="G3" t="n">
         <v>9.0626</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9143</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8922</v>
+        <v>0.5471</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0222</v>
+        <v>0.0502</v>
       </c>
       <c r="V3" t="n">
         <v>-0.337</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5189</v>
+        <v>4.7649</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3419</v>
+        <v>2.7264</v>
       </c>
       <c r="F4" t="n">
-        <v>1.177</v>
+        <v>2.0385</v>
       </c>
       <c r="G4" t="n">
-        <v>7.3458</v>
+        <v>4.8441</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4926</v>
+        <v>1.873</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8532</v>
+        <v>2.9711</v>
       </c>
       <c r="J4" t="n">
-        <v>6.7504</v>
+        <v>2.8263</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9258</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8247</v>
+        <v>2.1333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5954</v>
+        <v>2.0178</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5669</v>
+        <v>1.18</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0285</v>
+        <v>0.8378</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.9556</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2491</v>
+        <v>-1.4501</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9435</v>
+        <v>0.0717</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6944</v>
+        <v>-1.5218</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0956</v>
+        <v>1.5692</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6036</v>
+        <v>1.8107</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.508</v>
+        <v>-0.2414</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7481</v>
+        <v>3.942</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9904</v>
+        <v>2.7931</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7578</v>
+        <v>1.1489</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8441</v>
+        <v>7.3458</v>
       </c>
       <c r="H5" t="n">
-        <v>1.873</v>
+        <v>3.4926</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9711</v>
+        <v>3.8532</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8263</v>
+        <v>6.7504</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6929999999999999</v>
+        <v>2.9258</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1333</v>
+        <v>3.8247</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0178</v>
+        <v>0.5954</v>
       </c>
       <c r="N5" t="n">
-        <v>1.18</v>
+        <v>0.5669</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8378</v>
+        <v>0.0285</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1982</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R5" t="n">
         <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4669</v>
+        <v>-0.3278</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6643</v>
+        <v>0.3947</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8026</v>
+        <v>-0.7225</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5692</v>
+        <v>0.0956</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8107</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2414</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6323</v>
+        <v>1.2278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7562</v>
+        <v>0.7168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.876</v>
+        <v>0.511</v>
       </c>
       <c r="G6" t="n">
         <v>0.6921</v>
@@ -922,13 +922,13 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1554</v>
+        <v>-0.5599</v>
       </c>
       <c r="T6" t="n">
-        <v>0.18</v>
+        <v>0.1405</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3354</v>
+        <v>-0.7004</v>
       </c>
       <c r="V6" t="n">
         <v>0.6991000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6555</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.517</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.1726</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.3129</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.005</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.3079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.7475</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.1565</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.591</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.4346</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.1515</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.4102</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2305</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.6407</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1545</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1545</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1358</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0187</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0276</v>
+        <v>0.1826</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0888</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1164</v>
+        <v>0.1826</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3129</v>
+        <v>0.1358</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.005</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3079</v>
+        <v>0.1358</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7475</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1565</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.591</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4346</v>
+        <v>0.1358</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1515</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2831</v>
+        <v>0.1358</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0381</v>
+        <v>0.0468</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3413</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6968</v>
+        <v>0.0468</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1677</v>
+        <v>-1.1579</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2466</v>
+        <v>-1.1178</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0789</v>
+        <v>-0.0401</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4038</v>
+        <v>-0.4475</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.3617</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8015</v>
+        <v>-0.8093</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3908</v>
+        <v>-1.3381</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6319</v>
+        <v>-0.659</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2411</v>
+        <v>-0.6791</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7946</v>
+        <v>0.8905</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2342</v>
+        <v>1.0207</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5604</v>
+        <v>-0.1301</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.728</v>
+        <v>-0.7103</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1176</v>
+        <v>0.2203</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8456</v>
+        <v>-0.9306</v>
       </c>
       <c r="V11" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6215</v>
+        <v>-1.1895</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5253</v>
+        <v>-3.1842</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09619999999999999</v>
+        <v>1.9946</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4475</v>
+        <v>1.4038</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3617</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8093</v>
+        <v>0.8015</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3381</v>
+        <v>-0.3908</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.659</v>
+        <v>-0.6319</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6791</v>
+        <v>0.2411</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8905</v>
+        <v>1.7946</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0207</v>
+        <v>1.2342</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1301</v>
+        <v>0.5604</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.174</v>
+        <v>-0.7499</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1872</v>
+        <v>0.18</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9868</v>
+        <v>-0.9298</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8501</v>
+        <v>-2.2647</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0946</v>
+        <v>-1.7058</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.5589</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9561</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5202</v>
+        <v>0.1056</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9325</v>
+        <v>0.3213</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4123</v>
+        <v>-0.2157</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.976</v>
+        <v>-3.2753</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3044</v>
+        <v>-3.5476</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3284</v>
+        <v>0.2723</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9988</v>
@@ -1546,13 +1546,13 @@
         <v>0.5947</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5807</v>
+        <v>-0.8801</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2423</v>
+        <v>-0.0009</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8792</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.9722</v>
+        <v>-3.5086</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.3384</v>
+        <v>-2.9309</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6338</v>
+        <v>-0.5777</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1061</v>
@@ -1624,13 +1624,13 @@
         <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6931</v>
+        <v>-0.2294</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4257</v>
+        <v>-0.0183</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2673</v>
+        <v>-0.2112</v>
       </c>
       <c r="V15" t="n">
         <v>-1.182</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>20.182</v>
+        <v>20.8061</v>
       </c>
       <c r="E16" t="n">
-        <v>7.195500000000003</v>
+        <v>7.819700000000003</v>
       </c>
       <c r="F16" t="n">
         <v>12.9864</v>
@@ -1684,7 +1684,7 @@
         <v>13.2405</v>
       </c>
       <c r="M16" t="n">
-        <v>9.514999999999999</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>7.957199999999998</v>
@@ -1702,10 +1702,10 @@
         <v>15.8578</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.7089</v>
+        <v>-5.0848</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6531</v>
+        <v>2.277</v>
       </c>
       <c r="U16" t="n">
         <v>-7.3618</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4005</v>
+        <v>2.5028</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0264</v>
+        <v>2.3049</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3741</v>
+        <v>0.198</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1221</v>
+        <v>0.8216</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0979</v>
+        <v>2.0557</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0242</v>
+        <v>-1.2341</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2775</v>
+        <v>2.4658</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7189</v>
+        <v>1.7024</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5586</v>
+        <v>0.7634</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8446</v>
+        <v>-1.6442</v>
       </c>
       <c r="N17" t="n">
-        <v>0.621</v>
+        <v>0.3533</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4656</v>
+        <v>-1.9975</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9368</v>
+        <v>1.5354</v>
       </c>
       <c r="T17" t="n">
-        <v>3.304</v>
+        <v>1.5548</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3671</v>
+        <v>-0.0194</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1459</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1352</v>
+        <v>1.6966</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1011</v>
+        <v>0.9059</v>
       </c>
       <c r="F18" t="n">
-        <v>0.034</v>
+        <v>0.7907</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8216</v>
+        <v>-2.1221</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0557</v>
+        <v>-0.0979</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2341</v>
+        <v>-2.0242</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4658</v>
+        <v>-1.2775</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7024</v>
+        <v>-0.7189</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7634</v>
+        <v>-0.5586</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6442</v>
+        <v>-0.8446</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3533</v>
+        <v>0.621</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9975</v>
+        <v>-1.4656</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1677</v>
+        <v>2.2329</v>
       </c>
       <c r="T18" t="n">
-        <v>1.351</v>
+        <v>2.1834</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1833</v>
+        <v>0.0495</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1459</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7002</v>
+        <v>1.2754</v>
       </c>
       <c r="E19" t="n">
-        <v>1.025</v>
+        <v>0.6473</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6752</v>
+        <v>0.6281</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5861</v>
+        <v>-0.2393</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1511</v>
+        <v>0.059</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.435</v>
+        <v>-0.2983</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2742</v>
+        <v>0.8655</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6402</v>
+        <v>-0.8336</v>
       </c>
       <c r="L19" t="n">
-        <v>1.366</v>
+        <v>1.6991</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3119</v>
+        <v>-1.1048</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4891</v>
+        <v>0.8927</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.801</v>
+        <v>-1.9975</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9928</v>
+        <v>1.6354</v>
       </c>
       <c r="T19" t="n">
-        <v>3.0654</v>
+        <v>1.764</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9274</v>
+        <v>-0.1286</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0864</v>
+        <v>-0.1207</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-0.1207</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.506</v>
+        <v>0.2734</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6823</v>
+        <v>0.1082</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1764</v>
+        <v>0.1652</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6919</v>
+        <v>-2.5861</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.688</v>
+        <v>-1.1511</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0039</v>
+        <v>-1.435</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2974</v>
+        <v>-0.2742</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3494</v>
+        <v>-1.6402</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.366</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9893</v>
+        <v>-2.3119</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3386</v>
+        <v>0.4891</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6506</v>
+        <v>-2.801</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6825</v>
+        <v>2.566</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4554</v>
+        <v>2.1486</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2271</v>
+        <v>0.4174</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0704</v>
+        <v>1.0864</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0704</v>
+        <v>1.2071</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1914</v>
+        <v>-0.0406</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0361</v>
+        <v>0.173</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1554</v>
+        <v>-0.2136</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2393</v>
+        <v>-1.6919</v>
       </c>
       <c r="H22" t="n">
-        <v>0.059</v>
+        <v>-1.688</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2983</v>
+        <v>-0.0039</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8655</v>
+        <v>0.2974</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8336</v>
+        <v>-0.3494</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6991</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1048</v>
+        <v>-1.9893</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8927</v>
+        <v>-1.3386</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9975</v>
+        <v>-0.6506</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5514</v>
+        <v>0.1359</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1528</v>
+        <v>-0.054</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6014</v>
+        <v>0.1899</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1207</v>
+        <v>-0.0704</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4981</v>
+        <v>-0.7508</v>
       </c>
       <c r="E23" t="n">
         <v>-0.2319</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2662</v>
+        <v>-0.5189</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9073</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0722</v>
+        <v>0.8195</v>
       </c>
       <c r="T23" t="n">
         <v>0.4002</v>
       </c>
       <c r="U23" t="n">
-        <v>0.672</v>
+        <v>0.4193</v>
       </c>
       <c r="V23" t="n">
         <v>0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7219</v>
+        <v>-0.8192</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6503</v>
+        <v>-1.1596</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0717</v>
+        <v>0.3404</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6033</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0974</v>
+        <v>0.0001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5068</v>
+        <v>-0.0026</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4094</v>
+        <v>0.0027</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6036</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9468</v>
+        <v>-1.6131</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6301</v>
+        <v>-1.3245</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3167</v>
+        <v>-0.2887</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8518</v>
@@ -2404,13 +2404,13 @@
         <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2933</v>
+        <v>0.0404</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3873</v>
+        <v>-3.9399</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3093</v>
+        <v>-0.1055</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.078</v>
+        <v>-3.8344</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7722</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7272</v>
+        <v>-0.2798</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4771</v>
+        <v>-0.2734</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.25</v>
+        <v>-0.0065</v>
       </c>
       <c r="V26" t="n">
         <v>-3.2843</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.7818</v>
+        <v>-5.1099</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.5633</v>
+        <v>-3.3596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.2185</v>
+        <v>-1.7503</v>
       </c>
       <c r="G27" t="n">
         <v>-5.3139</v>
@@ -2560,13 +2560,13 @@
         <v>0.7929</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.5978</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9139</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6839</v>
+        <v>-0.2157</v>
       </c>
       <c r="V27" t="n">
         <v>0.337</v>
@@ -2581,7 +2581,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,73 +2593,73 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.7258</v>
+        <v>-6.0839</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.3658</v>
+        <v>-6.3851</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.36</v>
+        <v>0.3012</v>
       </c>
       <c r="G28" t="n">
-        <v>-4.0746</v>
+        <v>-5.2649</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1053</v>
+        <v>-1.7889</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.9693</v>
+        <v>-3.476</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.091</v>
+        <v>-4.0828</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1741</v>
+        <v>-1.9365</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.9169</v>
+        <v>-2.1463</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.9836</v>
+        <v>-1.1822</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.9312</v>
+        <v>0.1476</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.0524</v>
+        <v>-1.3298</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.9822</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R28" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.4888</v>
+        <v>0.8875</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5174</v>
+        <v>0.671</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.9714</v>
+        <v>0.2165</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8198</v>
+        <v>-0.1207</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.3873</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.6563</v>
+        <v>-6.1381</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.7094</v>
+        <v>-5.1621</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0531</v>
+        <v>-0.976</v>
       </c>
       <c r="G29" t="n">
-        <v>-5.2649</v>
+        <v>-4.0746</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.7889</v>
+        <v>-1.1053</v>
       </c>
       <c r="I29" t="n">
-        <v>-3.476</v>
+        <v>-2.9693</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.0828</v>
+        <v>-2.091</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.9365</v>
+        <v>-0.1741</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.1463</v>
+        <v>-1.9169</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.1822</v>
+        <v>-1.9836</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1476</v>
+        <v>-0.9312</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.3298</v>
+        <v>-1.0524</v>
       </c>
       <c r="P29" t="n">
-        <v>-1.5858</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6849</v>
+        <v>-0.9011</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.6533</v>
+        <v>-0.3137</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.0316</v>
+        <v>-0.5874</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1207</v>
+        <v>0.8198</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.1207</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="30">
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-20.182</v>
+        <v>-18.1446</v>
       </c>
       <c r="E30" t="n">
-        <v>-12.9865</v>
+        <v>-12.9863</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.1957</v>
+        <v>-5.158300000000001</v>
       </c>
       <c r="G30" t="n">
         <v>-27.0031</v>
@@ -2770,7 +2770,7 @@
         <v>-9.514900000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.957000000000001</v>
+        <v>-7.957</v>
       </c>
       <c r="L30" t="n">
         <v>-1.558</v>
@@ -2794,13 +2794,13 @@
         <v>17.8402</v>
       </c>
       <c r="S30" t="n">
-        <v>5.708800000000001</v>
+        <v>7.7463</v>
       </c>
       <c r="T30" t="n">
-        <v>7.3619</v>
+        <v>7.361700000000001</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.6529</v>
+        <v>0.3844999999999998</v>
       </c>
       <c r="V30" t="n">
         <v>-0.8701000000000002</v>
